--- a/certificates.xlsx
+++ b/certificates.xlsx
@@ -17,14 +17,14 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$484</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$481</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1927" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2408" uniqueCount="488">
   <si>
     <t>اسم المعلم</t>
   </si>
@@ -1479,6 +1479,15 @@
   </si>
   <si>
     <t>منال على سنوسي بشندي</t>
+  </si>
+  <si>
+    <t>نوع الشهادة</t>
+  </si>
+  <si>
+    <t>جديد</t>
+  </si>
+  <si>
+    <t>تجديد</t>
   </si>
 </sst>
 </file>
@@ -1534,7 +1543,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1557,12 +1566,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1604,12 +1624,15 @@
     <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Sheet1" xfId="1"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1627,48 +1650,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFC7CE"/>
-          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1972,7 +1953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G481"/>
+  <dimension ref="A1:H481"/>
   <sheetFormatPr defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1982,9 +1963,10 @@
     <col min="5" max="5" width="29.28515625" style="3" customWidth="1"/>
     <col min="6" max="6" width="16.140625" style="5" customWidth="1"/>
     <col min="7" max="7" width="35.5703125" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>352</v>
       </c>
@@ -2006,8 +1988,11 @@
       <c r="G1" s="9" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H1" s="15" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>2692</v>
       </c>
@@ -2029,8 +2014,11 @@
       <c r="G2" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
         <v>2852</v>
       </c>
@@ -2052,8 +2040,11 @@
       <c r="G3" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <v>2723</v>
       </c>
@@ -2075,8 +2066,11 @@
       <c r="G4" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>2860</v>
       </c>
@@ -2098,8 +2092,11 @@
       <c r="G5" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>2705</v>
       </c>
@@ -2121,8 +2118,11 @@
       <c r="G6" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>2938</v>
       </c>
@@ -2144,8 +2144,11 @@
       <c r="G7" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>2923</v>
       </c>
@@ -2167,8 +2170,11 @@
       <c r="G8" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>2831</v>
       </c>
@@ -2190,8 +2196,11 @@
       <c r="G9" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>3213</v>
       </c>
@@ -2213,8 +2222,11 @@
       <c r="G10" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>2815</v>
       </c>
@@ -2236,8 +2248,11 @@
       <c r="G11" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>3214</v>
       </c>
@@ -2259,8 +2274,11 @@
       <c r="G12" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>89</v>
       </c>
@@ -2282,8 +2300,11 @@
       <c r="G13" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>2756</v>
       </c>
@@ -2305,8 +2326,11 @@
       <c r="G14" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>89</v>
       </c>
@@ -2328,8 +2352,11 @@
       <c r="G15" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>2880</v>
       </c>
@@ -2351,8 +2378,11 @@
       <c r="G16" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>2702</v>
       </c>
@@ -2374,8 +2404,11 @@
       <c r="G17" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>2957</v>
       </c>
@@ -2397,8 +2430,11 @@
       <c r="G18" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>2683</v>
       </c>
@@ -2420,8 +2456,11 @@
       <c r="G19" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>2787</v>
       </c>
@@ -2443,8 +2482,11 @@
       <c r="G20" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>2874</v>
       </c>
@@ -2466,8 +2508,11 @@
       <c r="G21" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>2945</v>
       </c>
@@ -2489,8 +2534,11 @@
       <c r="G22" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>2746</v>
       </c>
@@ -2512,8 +2560,11 @@
       <c r="G23" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>2811</v>
       </c>
@@ -2535,8 +2586,11 @@
       <c r="G24" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>2762</v>
       </c>
@@ -2558,8 +2612,11 @@
       <c r="G25" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>2778</v>
       </c>
@@ -2581,8 +2638,11 @@
       <c r="G26" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>2849</v>
       </c>
@@ -2604,8 +2664,11 @@
       <c r="G27" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H27" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>2829</v>
       </c>
@@ -2627,8 +2690,11 @@
       <c r="G28" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>2832</v>
       </c>
@@ -2650,8 +2716,11 @@
       <c r="G29" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>3217</v>
       </c>
@@ -2673,8 +2742,11 @@
       <c r="G30" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>2965</v>
       </c>
@@ -2696,8 +2768,11 @@
       <c r="G31" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>2775</v>
       </c>
@@ -2719,8 +2794,11 @@
       <c r="G32" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H32" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>2866</v>
       </c>
@@ -2742,8 +2820,11 @@
       <c r="G33" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H33" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>3036</v>
       </c>
@@ -2765,8 +2846,11 @@
       <c r="G34" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H34" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>2939</v>
       </c>
@@ -2788,8 +2872,11 @@
       <c r="G35" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H35" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>2826</v>
       </c>
@@ -2811,8 +2898,11 @@
       <c r="G36" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H36" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>2684</v>
       </c>
@@ -2834,8 +2924,11 @@
       <c r="G37" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H37" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>2745</v>
       </c>
@@ -2857,8 +2950,11 @@
       <c r="G38" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H38" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>89</v>
       </c>
@@ -2880,8 +2976,11 @@
       <c r="G39" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H39" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>89</v>
       </c>
@@ -2903,8 +3002,11 @@
       <c r="G40" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H40" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>3226</v>
       </c>
@@ -2926,8 +3028,11 @@
       <c r="G41" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H41" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>89</v>
       </c>
@@ -2949,8 +3054,11 @@
       <c r="G42" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H42" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>2838</v>
       </c>
@@ -2972,8 +3080,11 @@
       <c r="G43" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H43" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>2695</v>
       </c>
@@ -2995,8 +3106,11 @@
       <c r="G44" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H44" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>2808</v>
       </c>
@@ -3018,8 +3132,11 @@
       <c r="G45" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H45" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>2748</v>
       </c>
@@ -3041,8 +3158,11 @@
       <c r="G46" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H46" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>2819</v>
       </c>
@@ -3064,8 +3184,11 @@
       <c r="G47" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H47" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>2820</v>
       </c>
@@ -3087,8 +3210,11 @@
       <c r="G48" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H48" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>2840</v>
       </c>
@@ -3110,8 +3236,11 @@
       <c r="G49" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H49" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>2948</v>
       </c>
@@ -3133,8 +3262,11 @@
       <c r="G50" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H50" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>2916</v>
       </c>
@@ -3156,8 +3288,11 @@
       <c r="G51" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H51" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>2773</v>
       </c>
@@ -3179,8 +3314,11 @@
       <c r="G52" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H52" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>2901</v>
       </c>
@@ -3202,8 +3340,11 @@
       <c r="G53" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H53" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>3232</v>
       </c>
@@ -3225,8 +3366,11 @@
       <c r="G54" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H54" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>2682</v>
       </c>
@@ -3248,8 +3392,11 @@
       <c r="G55" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H55" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>2701</v>
       </c>
@@ -3271,8 +3418,11 @@
       <c r="G56" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H56" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>2799</v>
       </c>
@@ -3294,8 +3444,11 @@
       <c r="G57" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H57" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>2800</v>
       </c>
@@ -3317,8 +3470,11 @@
       <c r="G58" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H58" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>89</v>
       </c>
@@ -3340,8 +3496,11 @@
       <c r="G59" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H59" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>2893</v>
       </c>
@@ -3363,8 +3522,11 @@
       <c r="G60" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H60" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>2747</v>
       </c>
@@ -3386,8 +3548,11 @@
       <c r="G61" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H61" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>89</v>
       </c>
@@ -3409,8 +3574,11 @@
       <c r="G62" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H62" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>2722</v>
       </c>
@@ -3432,8 +3600,11 @@
       <c r="G63" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H63" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>2922</v>
       </c>
@@ -3455,8 +3626,11 @@
       <c r="G64" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H64" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>2676</v>
       </c>
@@ -3478,8 +3652,11 @@
       <c r="G65" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H65" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>2812</v>
       </c>
@@ -3501,8 +3678,11 @@
       <c r="G66" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H66" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>3248</v>
       </c>
@@ -3524,8 +3704,11 @@
       <c r="G67" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H67" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>2719</v>
       </c>
@@ -3547,8 +3730,11 @@
       <c r="G68" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H68" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>89</v>
       </c>
@@ -3570,8 +3756,11 @@
       <c r="G69" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H69" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>3240</v>
       </c>
@@ -3593,8 +3782,11 @@
       <c r="G70" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H70" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>3222</v>
       </c>
@@ -3616,8 +3808,11 @@
       <c r="G71" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H71" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>89</v>
       </c>
@@ -3639,8 +3834,11 @@
       <c r="G72" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H72" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>2754</v>
       </c>
@@ -3662,8 +3860,11 @@
       <c r="G73" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H73" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>3101</v>
       </c>
@@ -3685,8 +3886,11 @@
       <c r="G74" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H74" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>2855</v>
       </c>
@@ -3708,8 +3912,11 @@
       <c r="G75" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H75" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>2867</v>
       </c>
@@ -3731,8 +3938,11 @@
       <c r="G76" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H76" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>2793</v>
       </c>
@@ -3754,8 +3964,11 @@
       <c r="G77" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H77" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>2908</v>
       </c>
@@ -3777,8 +3990,11 @@
       <c r="G78" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H78" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>2724</v>
       </c>
@@ -3800,8 +4016,11 @@
       <c r="G79" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H79" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>2858</v>
       </c>
@@ -3823,8 +4042,11 @@
       <c r="G80" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H80" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>89</v>
       </c>
@@ -3846,8 +4068,11 @@
       <c r="G81" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H81" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>2810</v>
       </c>
@@ -3869,8 +4094,11 @@
       <c r="G82" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H82" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>2782</v>
       </c>
@@ -3892,8 +4120,11 @@
       <c r="G83" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H83" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>2887</v>
       </c>
@@ -3915,8 +4146,11 @@
       <c r="G84" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H84" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>2732</v>
       </c>
@@ -3938,8 +4172,11 @@
       <c r="G85" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H85" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>3049</v>
       </c>
@@ -3961,8 +4198,11 @@
       <c r="G86" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H86" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>2806</v>
       </c>
@@ -3984,8 +4224,11 @@
       <c r="G87" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H87" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>2677</v>
       </c>
@@ -4007,8 +4250,11 @@
       <c r="G88" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H88" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>2780</v>
       </c>
@@ -4030,8 +4276,11 @@
       <c r="G89" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H89" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>2952</v>
       </c>
@@ -4053,8 +4302,11 @@
       <c r="G90" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H90" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>2687</v>
       </c>
@@ -4076,8 +4328,11 @@
       <c r="G91" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H91" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>2764</v>
       </c>
@@ -4099,8 +4354,11 @@
       <c r="G92" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H92" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>89</v>
       </c>
@@ -4122,8 +4380,11 @@
       <c r="G93" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H93" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>2911</v>
       </c>
@@ -4145,8 +4406,11 @@
       <c r="G94" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H94" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>2807</v>
       </c>
@@ -4168,8 +4432,11 @@
       <c r="G95" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H95" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>2830</v>
       </c>
@@ -4191,8 +4458,11 @@
       <c r="G96" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H96" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>2951</v>
       </c>
@@ -4214,8 +4484,11 @@
       <c r="G97" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H97" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>89</v>
       </c>
@@ -4237,8 +4510,11 @@
       <c r="G98" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H98" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>2917</v>
       </c>
@@ -4260,8 +4536,11 @@
       <c r="G99" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H99" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>3030</v>
       </c>
@@ -4283,8 +4562,11 @@
       <c r="G100" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H100" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>89</v>
       </c>
@@ -4306,8 +4588,11 @@
       <c r="G101" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H101" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>2864</v>
       </c>
@@ -4329,8 +4614,11 @@
       <c r="G102" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H102" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>2720</v>
       </c>
@@ -4352,8 +4640,11 @@
       <c r="G103" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H103" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>2959</v>
       </c>
@@ -4375,8 +4666,11 @@
       <c r="G104" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H104" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>2742</v>
       </c>
@@ -4398,8 +4692,11 @@
       <c r="G105" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H105" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>89</v>
       </c>
@@ -4421,8 +4718,11 @@
       <c r="G106" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H106" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>2804</v>
       </c>
@@ -4444,8 +4744,11 @@
       <c r="G107" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H107" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>89</v>
       </c>
@@ -4467,8 +4770,11 @@
       <c r="G108" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H108" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>2821</v>
       </c>
@@ -4490,8 +4796,11 @@
       <c r="G109" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H109" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>2822</v>
       </c>
@@ -4513,8 +4822,11 @@
       <c r="G110" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H110" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>3063</v>
       </c>
@@ -4536,8 +4848,11 @@
       <c r="G111" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H111" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>2709</v>
       </c>
@@ -4559,8 +4874,11 @@
       <c r="G112" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H112" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>89</v>
       </c>
@@ -4582,8 +4900,11 @@
       <c r="G113" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H113" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>89</v>
       </c>
@@ -4605,8 +4926,11 @@
       <c r="G114" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H114" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>2961</v>
       </c>
@@ -4628,8 +4952,11 @@
       <c r="G115" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H115" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>2942</v>
       </c>
@@ -4651,8 +4978,11 @@
       <c r="G116" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H116" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>3254</v>
       </c>
@@ -4674,8 +5004,11 @@
       <c r="G117" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H117" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>2721</v>
       </c>
@@ -4697,8 +5030,11 @@
       <c r="G118" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H118" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>2954</v>
       </c>
@@ -4720,8 +5056,11 @@
       <c r="G119" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H119" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>2875</v>
       </c>
@@ -4743,8 +5082,11 @@
       <c r="G120" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H120" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>2898</v>
       </c>
@@ -4766,8 +5108,11 @@
       <c r="G121" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H121" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>2958</v>
       </c>
@@ -4789,8 +5134,11 @@
       <c r="G122" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H122" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>2853</v>
       </c>
@@ -4812,8 +5160,11 @@
       <c r="G123" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H123" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>89</v>
       </c>
@@ -4835,8 +5186,11 @@
       <c r="G124" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H124" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>89</v>
       </c>
@@ -4858,8 +5212,11 @@
       <c r="G125" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H125" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>89</v>
       </c>
@@ -4881,8 +5238,11 @@
       <c r="G126" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H126" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>89</v>
       </c>
@@ -4904,8 +5264,11 @@
       <c r="G127" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H127" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>3242</v>
       </c>
@@ -4927,8 +5290,11 @@
       <c r="G128" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H128" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>3227</v>
       </c>
@@ -4950,8 +5316,11 @@
       <c r="G129" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H129" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>3206</v>
       </c>
@@ -4973,8 +5342,11 @@
       <c r="G130" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H130" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>2686</v>
       </c>
@@ -4996,8 +5368,11 @@
       <c r="G131" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H131" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
         <v>2876</v>
       </c>
@@ -5019,8 +5394,11 @@
       <c r="G132" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H132" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6">
         <v>2706</v>
       </c>
@@ -5042,8 +5420,11 @@
       <c r="G133" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H133" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6">
         <v>2836</v>
       </c>
@@ -5065,8 +5446,11 @@
       <c r="G134" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H134" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
         <v>2861</v>
       </c>
@@ -5088,8 +5472,11 @@
       <c r="G135" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H135" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6">
         <v>2801</v>
       </c>
@@ -5111,8 +5498,11 @@
       <c r="G136" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H136" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
         <v>2715</v>
       </c>
@@ -5134,8 +5524,11 @@
       <c r="G137" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H137" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6">
         <v>3237</v>
       </c>
@@ -5157,8 +5550,11 @@
       <c r="G138" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H138" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6">
         <v>2733</v>
       </c>
@@ -5180,8 +5576,11 @@
       <c r="G139" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H139" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6">
         <v>89</v>
       </c>
@@ -5203,8 +5602,11 @@
       <c r="G140" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H140" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
         <v>89</v>
       </c>
@@ -5226,8 +5628,11 @@
       <c r="G141" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H141" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6">
         <v>89</v>
       </c>
@@ -5249,8 +5654,11 @@
       <c r="G142" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H142" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6">
         <v>2856</v>
       </c>
@@ -5272,8 +5680,11 @@
       <c r="G143" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H143" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
         <v>2847</v>
       </c>
@@ -5295,8 +5706,11 @@
       <c r="G144" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H144" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6">
         <v>2998</v>
       </c>
@@ -5318,8 +5732,11 @@
       <c r="G145" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H145" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6">
         <v>3076</v>
       </c>
@@ -5341,8 +5758,11 @@
       <c r="G146" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="147" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H146" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
         <v>89</v>
       </c>
@@ -5364,8 +5784,11 @@
       <c r="G147" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="148" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H147" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6">
         <v>2774</v>
       </c>
@@ -5387,8 +5810,11 @@
       <c r="G148" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H148" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6">
         <v>2877</v>
       </c>
@@ -5410,8 +5836,11 @@
       <c r="G149" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="150" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H149" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6">
         <v>2789</v>
       </c>
@@ -5433,8 +5862,11 @@
       <c r="G150" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H150" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
         <v>89</v>
       </c>
@@ -5456,8 +5888,11 @@
       <c r="G151" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H151" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6">
         <v>2818</v>
       </c>
@@ -5479,8 +5914,11 @@
       <c r="G152" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H152" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6">
         <v>2743</v>
       </c>
@@ -5502,8 +5940,11 @@
       <c r="G153" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H153" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6">
         <v>89</v>
       </c>
@@ -5525,8 +5966,11 @@
       <c r="G154" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H154" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6">
         <v>3211</v>
       </c>
@@ -5548,8 +5992,11 @@
       <c r="G155" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H155" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6">
         <v>3094</v>
       </c>
@@ -5571,8 +6018,11 @@
       <c r="G156" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H156" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
         <v>2955</v>
       </c>
@@ -5594,8 +6044,11 @@
       <c r="G157" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H157" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6">
         <v>2678</v>
       </c>
@@ -5617,8 +6070,11 @@
       <c r="G158" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H158" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6">
         <v>2679</v>
       </c>
@@ -5640,8 +6096,11 @@
       <c r="G159" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H159" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
         <v>3011</v>
       </c>
@@ -5663,8 +6122,11 @@
       <c r="G160" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="161" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H160" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6">
         <v>3221</v>
       </c>
@@ -5686,8 +6148,11 @@
       <c r="G161" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="162" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H161" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6">
         <v>89</v>
       </c>
@@ -5709,8 +6174,11 @@
       <c r="G162" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="163" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H162" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6">
         <v>2999</v>
       </c>
@@ -5732,8 +6200,11 @@
       <c r="G163" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="164" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H163" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
         <v>89</v>
       </c>
@@ -5755,8 +6226,11 @@
       <c r="G164" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="165" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H164" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6">
         <v>89</v>
       </c>
@@ -5778,8 +6252,11 @@
       <c r="G165" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="166" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H165" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6">
         <v>2712</v>
       </c>
@@ -5801,8 +6278,11 @@
       <c r="G166" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="167" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H166" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
         <v>3207</v>
       </c>
@@ -5824,8 +6304,11 @@
       <c r="G167" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="168" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H167" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6">
         <v>2785</v>
       </c>
@@ -5847,8 +6330,11 @@
       <c r="G168" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H168" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
         <v>2786</v>
       </c>
@@ -5870,8 +6356,11 @@
       <c r="G169" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="170" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H169" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6">
         <v>3203</v>
       </c>
@@ -5893,8 +6382,11 @@
       <c r="G170" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="171" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H170" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6">
         <v>2910</v>
       </c>
@@ -5916,8 +6408,11 @@
       <c r="G171" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="172" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H171" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
         <v>2897</v>
       </c>
@@ -5939,8 +6434,11 @@
       <c r="G172" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="173" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H172" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6">
         <v>2891</v>
       </c>
@@ -5962,8 +6460,11 @@
       <c r="G173" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="174" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H173" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6">
         <v>3223</v>
       </c>
@@ -5985,8 +6486,11 @@
       <c r="G174" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="175" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H174" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6">
         <v>89</v>
       </c>
@@ -6008,8 +6512,11 @@
       <c r="G175" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H175" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
         <v>2749</v>
       </c>
@@ -6031,8 +6538,11 @@
       <c r="G176" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="177" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H176" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6">
         <v>3255</v>
       </c>
@@ -6054,8 +6564,11 @@
       <c r="G177" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="178" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H177" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6">
         <v>89</v>
       </c>
@@ -6077,8 +6590,11 @@
       <c r="G178" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="179" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H178" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
         <v>2795</v>
       </c>
@@ -6100,8 +6616,11 @@
       <c r="G179" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="180" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H179" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6">
         <v>2770</v>
       </c>
@@ -6123,8 +6642,11 @@
       <c r="G180" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H180" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6">
         <v>2771</v>
       </c>
@@ -6146,8 +6668,11 @@
       <c r="G181" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="182" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H181" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6">
         <v>3224</v>
       </c>
@@ -6169,8 +6694,11 @@
       <c r="G182" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="183" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H182" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
         <v>2934</v>
       </c>
@@ -6192,8 +6720,11 @@
       <c r="G183" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="184" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H183" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6">
         <v>2841</v>
       </c>
@@ -6215,8 +6746,11 @@
       <c r="G184" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="185" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H184" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6">
         <v>3204</v>
       </c>
@@ -6238,8 +6772,11 @@
       <c r="G185" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="186" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H185" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6">
         <v>3251</v>
       </c>
@@ -6261,8 +6798,11 @@
       <c r="G186" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="187" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H186" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6">
         <v>2907</v>
       </c>
@@ -6284,8 +6824,11 @@
       <c r="G187" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="188" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H187" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6">
         <v>3263</v>
       </c>
@@ -6307,8 +6850,11 @@
       <c r="G188" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="189" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H188" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6">
         <v>3264</v>
       </c>
@@ -6330,8 +6876,11 @@
       <c r="G189" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H189" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
         <v>89</v>
       </c>
@@ -6353,8 +6902,11 @@
       <c r="G190" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H190" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6">
         <v>89</v>
       </c>
@@ -6376,8 +6928,11 @@
       <c r="G191" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H191" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6">
         <v>89</v>
       </c>
@@ -6399,8 +6954,11 @@
       <c r="G192" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H192" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
         <v>2862</v>
       </c>
@@ -6422,8 +6980,11 @@
       <c r="G193" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H193" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6">
         <v>2947</v>
       </c>
@@ -6445,8 +7006,11 @@
       <c r="G194" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H194" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6">
         <v>2894</v>
       </c>
@@ -6468,8 +7032,11 @@
       <c r="G195" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="196" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H195" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6">
         <v>89</v>
       </c>
@@ -6491,8 +7058,11 @@
       <c r="G196" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="197" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H196" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6">
         <v>3111</v>
       </c>
@@ -6514,8 +7084,11 @@
       <c r="G197" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H197" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
         <v>2886</v>
       </c>
@@ -6537,8 +7110,11 @@
       <c r="G198" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="199" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H198" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6">
         <v>2794</v>
       </c>
@@ -6560,8 +7136,11 @@
       <c r="G199" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="200" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H199" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6">
         <v>2739</v>
       </c>
@@ -6583,8 +7162,11 @@
       <c r="G200" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="201" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H200" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6">
         <v>2740</v>
       </c>
@@ -6606,8 +7188,11 @@
       <c r="G201" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H201" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6">
         <v>3083</v>
       </c>
@@ -6629,8 +7214,11 @@
       <c r="G202" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="203" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H202" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
         <v>89</v>
       </c>
@@ -6652,8 +7240,11 @@
       <c r="G203" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H203" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6">
         <v>2914</v>
       </c>
@@ -6675,8 +7266,11 @@
       <c r="G204" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="205" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H204" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
         <v>3228</v>
       </c>
@@ -6698,8 +7292,11 @@
       <c r="G205" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="206" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H205" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6">
         <v>2685</v>
       </c>
@@ -6721,8 +7318,11 @@
       <c r="G206" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H206" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6">
         <v>3225</v>
       </c>
@@ -6744,8 +7344,11 @@
       <c r="G207" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="208" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H207" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6">
         <v>2837</v>
       </c>
@@ -6767,8 +7370,11 @@
       <c r="G208" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="209" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H208" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
         <v>2868</v>
       </c>
@@ -6790,8 +7396,11 @@
       <c r="G209" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H209" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6">
         <v>2946</v>
       </c>
@@ -6813,8 +7422,11 @@
       <c r="G210" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="211" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H210" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6">
         <v>89</v>
       </c>
@@ -6836,8 +7448,11 @@
       <c r="G211" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H211" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6">
         <v>2960</v>
       </c>
@@ -6859,8 +7474,11 @@
       <c r="G212" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H212" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
         <v>2935</v>
       </c>
@@ -6882,8 +7500,11 @@
       <c r="G213" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H213" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6">
         <v>3040</v>
       </c>
@@ -6905,8 +7526,11 @@
       <c r="G214" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="215" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H214" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6">
         <v>2919</v>
       </c>
@@ -6928,8 +7552,11 @@
       <c r="G215" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="216" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H215" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6">
         <v>2953</v>
       </c>
@@ -6951,8 +7578,11 @@
       <c r="G216" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="217" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H216" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
         <v>2827</v>
       </c>
@@ -6974,8 +7604,11 @@
       <c r="G217" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="218" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H217" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6">
         <v>3025</v>
       </c>
@@ -6997,8 +7630,11 @@
       <c r="G218" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="219" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H218" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6">
         <v>2763</v>
       </c>
@@ -7020,8 +7656,11 @@
       <c r="G219" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="220" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H219" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6">
         <v>2926</v>
       </c>
@@ -7043,8 +7682,11 @@
       <c r="G220" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="221" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H220" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
         <v>89</v>
       </c>
@@ -7066,8 +7708,11 @@
       <c r="G221" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="222" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H221" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6">
         <v>2878</v>
       </c>
@@ -7089,8 +7734,11 @@
       <c r="G222" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="223" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H222" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6">
         <v>89</v>
       </c>
@@ -7112,8 +7760,11 @@
       <c r="G223" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="224" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H223" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6">
         <v>2850</v>
       </c>
@@ -7135,8 +7786,11 @@
       <c r="G224" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="225" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H224" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6">
         <v>89</v>
       </c>
@@ -7158,8 +7812,11 @@
       <c r="G225" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="226" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H225" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
         <v>3069</v>
       </c>
@@ -7181,8 +7838,11 @@
       <c r="G226" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="227" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H226" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6">
         <v>2843</v>
       </c>
@@ -7204,8 +7864,11 @@
       <c r="G227" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="228" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H227" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6">
         <v>2693</v>
       </c>
@@ -7227,8 +7890,11 @@
       <c r="G228" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="229" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H228" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6">
         <v>3097</v>
       </c>
@@ -7250,8 +7916,11 @@
       <c r="G229" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="230" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H229" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6">
         <v>2966</v>
       </c>
@@ -7273,8 +7942,11 @@
       <c r="G230" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H230" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6">
         <v>89</v>
       </c>
@@ -7296,8 +7968,11 @@
       <c r="G231" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H231" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
         <v>3244</v>
       </c>
@@ -7319,8 +7994,11 @@
       <c r="G232" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H232" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6">
         <v>3245</v>
       </c>
@@ -7342,8 +8020,11 @@
       <c r="G233" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="234" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H233" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6">
         <v>3246</v>
       </c>
@@ -7365,8 +8046,11 @@
       <c r="G234" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="235" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H234" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
         <v>2882</v>
       </c>
@@ -7388,8 +8072,11 @@
       <c r="G235" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="236" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H235" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6">
         <v>2927</v>
       </c>
@@ -7411,8 +8098,11 @@
       <c r="G236" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H236" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6">
         <v>2912</v>
       </c>
@@ -7434,8 +8124,11 @@
       <c r="G237" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="238" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H237" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6">
         <v>3200</v>
       </c>
@@ -7457,8 +8150,11 @@
       <c r="G238" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="239" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H238" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
         <v>2696</v>
       </c>
@@ -7480,8 +8176,11 @@
       <c r="G239" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="240" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H239" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6">
         <v>2697</v>
       </c>
@@ -7503,8 +8202,11 @@
       <c r="G240" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="241" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H240" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6">
         <v>89</v>
       </c>
@@ -7526,8 +8228,11 @@
       <c r="G241" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="242" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H241" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6">
         <v>2902</v>
       </c>
@@ -7549,8 +8254,11 @@
       <c r="G242" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="243" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H242" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6">
         <v>2903</v>
       </c>
@@ -7572,8 +8280,11 @@
       <c r="G243" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H243" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6">
         <v>2675</v>
       </c>
@@ -7595,8 +8306,11 @@
       <c r="G244" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H244" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
         <v>2776</v>
       </c>
@@ -7618,8 +8332,11 @@
       <c r="G245" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="246" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H245" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6">
         <v>2892</v>
       </c>
@@ -7641,8 +8358,11 @@
       <c r="G246" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="247" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H246" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6">
         <v>2700</v>
       </c>
@@ -7664,8 +8384,11 @@
       <c r="G247" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="248" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H247" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6">
         <v>2809</v>
       </c>
@@ -7687,8 +8410,11 @@
       <c r="G248" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H248" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
         <v>89</v>
       </c>
@@ -7710,8 +8436,11 @@
       <c r="G249" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="250" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H249" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6">
         <v>2755</v>
       </c>
@@ -7733,8 +8462,11 @@
       <c r="G250" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H250" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
         <v>2949</v>
       </c>
@@ -7756,8 +8488,11 @@
       <c r="G251" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="252" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H251" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6">
         <v>3249</v>
       </c>
@@ -7779,8 +8514,11 @@
       <c r="G252" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="253" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H252" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6">
         <v>2728</v>
       </c>
@@ -7802,8 +8540,11 @@
       <c r="G253" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="254" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H253" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6">
         <v>2783</v>
       </c>
@@ -7825,8 +8566,11 @@
       <c r="G254" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="255" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H254" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
         <v>2784</v>
       </c>
@@ -7848,8 +8592,11 @@
       <c r="G255" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="256" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H255" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6">
         <v>2738</v>
       </c>
@@ -7871,8 +8618,11 @@
       <c r="G256" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="257" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H256" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6">
         <v>89</v>
       </c>
@@ -7894,8 +8644,11 @@
       <c r="G257" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="258" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H257" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6">
         <v>2913</v>
       </c>
@@ -7917,8 +8670,11 @@
       <c r="G258" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="259" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H258" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
         <v>89</v>
       </c>
@@ -7940,8 +8696,11 @@
       <c r="G259" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="260" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H259" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6">
         <v>2896</v>
       </c>
@@ -7963,8 +8722,11 @@
       <c r="G260" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="261" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H260" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6">
         <v>2765</v>
       </c>
@@ -7986,8 +8748,11 @@
       <c r="G261" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="262" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H261" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6">
         <v>2805</v>
       </c>
@@ -8009,8 +8774,11 @@
       <c r="G262" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="263" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H262" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
         <v>2729</v>
       </c>
@@ -8032,8 +8800,11 @@
       <c r="G263" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="264" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H263" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6">
         <v>89</v>
       </c>
@@ -8055,8 +8826,11 @@
       <c r="G264" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="265" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H264" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6">
         <v>89</v>
       </c>
@@ -8078,8 +8852,11 @@
       <c r="G265" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="266" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H265" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6">
         <v>3212</v>
       </c>
@@ -8101,8 +8878,11 @@
       <c r="G266" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="267" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H266" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
         <v>89</v>
       </c>
@@ -8124,8 +8904,11 @@
       <c r="G267" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="268" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H267" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6">
         <v>2714</v>
       </c>
@@ -8147,8 +8930,11 @@
       <c r="G268" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="269" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H268" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6">
         <v>2699</v>
       </c>
@@ -8170,8 +8956,11 @@
       <c r="G269" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="270" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H269" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
         <v>2803</v>
       </c>
@@ -8193,8 +8982,11 @@
       <c r="G270" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="271" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H270" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6">
         <v>2681</v>
       </c>
@@ -8216,8 +9008,11 @@
       <c r="G271" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="272" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H271" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6">
         <v>2930</v>
       </c>
@@ -8239,8 +9034,11 @@
       <c r="G272" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="273" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H272" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
         <v>89</v>
       </c>
@@ -8262,8 +9060,11 @@
       <c r="G273" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="274" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H273" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6">
         <v>2964</v>
       </c>
@@ -8285,8 +9086,11 @@
       <c r="G274" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="275" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H274" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6">
         <v>2698</v>
       </c>
@@ -8308,8 +9112,11 @@
       <c r="G275" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="276" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H275" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6">
         <v>2750</v>
       </c>
@@ -8331,8 +9138,11 @@
       <c r="G276" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H276" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
         <v>2906</v>
       </c>
@@ -8354,8 +9164,11 @@
       <c r="G277" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="278" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H277" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6">
         <v>2969</v>
       </c>
@@ -8377,8 +9190,11 @@
       <c r="G278" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="279" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H278" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6">
         <v>89</v>
       </c>
@@ -8400,8 +9216,11 @@
       <c r="G279" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="280" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H279" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6">
         <v>2694</v>
       </c>
@@ -8423,8 +9242,11 @@
       <c r="G280" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="281" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H280" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
         <v>3260</v>
       </c>
@@ -8446,8 +9268,11 @@
       <c r="G281" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="282" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H281" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6">
         <v>2835</v>
       </c>
@@ -8469,8 +9294,11 @@
       <c r="G282" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="283" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H282" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6">
         <v>2915</v>
       </c>
@@ -8492,8 +9320,11 @@
       <c r="G283" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="284" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H283" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6">
         <v>3236</v>
       </c>
@@ -8515,8 +9346,11 @@
       <c r="G284" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="285" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H284" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
         <v>2883</v>
       </c>
@@ -8538,8 +9372,11 @@
       <c r="G285" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="286" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H285" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6">
         <v>2870</v>
       </c>
@@ -8561,8 +9398,11 @@
       <c r="G286" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="287" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H286" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
         <v>3229</v>
       </c>
@@ -8584,8 +9424,11 @@
       <c r="G287" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="288" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H287" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6">
         <v>2726</v>
       </c>
@@ -8607,8 +9450,11 @@
       <c r="G288" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="289" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H288" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6">
         <v>3078</v>
       </c>
@@ -8630,8 +9476,11 @@
       <c r="G289" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="290" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H289" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6">
         <v>3208</v>
       </c>
@@ -8653,8 +9502,11 @@
       <c r="G290" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H290" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
         <v>3209</v>
       </c>
@@ -8676,8 +9528,11 @@
       <c r="G291" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="292" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H291" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6">
         <v>3238</v>
       </c>
@@ -8699,8 +9554,11 @@
       <c r="G292" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="293" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H292" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6">
         <v>3239</v>
       </c>
@@ -8722,8 +9580,11 @@
       <c r="G293" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="294" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H293" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6">
         <v>2884</v>
       </c>
@@ -8745,8 +9606,11 @@
       <c r="G294" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="295" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H294" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
         <v>2688</v>
       </c>
@@ -8768,8 +9632,11 @@
       <c r="G295" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="296" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H295" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6">
         <v>2689</v>
       </c>
@@ -8791,8 +9658,11 @@
       <c r="G296" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H296" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6">
         <v>3065</v>
       </c>
@@ -8814,8 +9684,11 @@
       <c r="G297" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="298" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H297" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6">
         <v>89</v>
       </c>
@@ -8837,8 +9710,11 @@
       <c r="G298" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="299" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H298" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
         <v>2727</v>
       </c>
@@ -8860,8 +9736,11 @@
       <c r="G299" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="300" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H299" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6">
         <v>89</v>
       </c>
@@ -8883,8 +9762,11 @@
       <c r="G300" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="301" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H300" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6">
         <v>2889</v>
       </c>
@@ -8906,8 +9788,11 @@
       <c r="G301" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="302" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H301" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6">
         <v>2816</v>
       </c>
@@ -8929,8 +9814,11 @@
       <c r="G302" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="303" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H302" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>2744</v>
       </c>
@@ -8952,8 +9840,11 @@
       <c r="G303" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="304" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H303" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>2956</v>
       </c>
@@ -8975,8 +9866,11 @@
       <c r="G304" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="305" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H304" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6">
         <v>3256</v>
       </c>
@@ -8998,8 +9892,11 @@
       <c r="G305" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="306" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H305" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6">
         <v>2703</v>
       </c>
@@ -9021,8 +9918,11 @@
       <c r="G306" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="307" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H306" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6">
         <v>2704</v>
       </c>
@@ -9044,8 +9944,11 @@
       <c r="G307" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="308" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H307" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6">
         <v>89</v>
       </c>
@@ -9067,8 +9970,11 @@
       <c r="G308" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="309" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H308" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6">
         <v>3241</v>
       </c>
@@ -9090,8 +9996,11 @@
       <c r="G309" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="310" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H309" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6">
         <v>2918</v>
       </c>
@@ -9113,8 +10022,11 @@
       <c r="G310" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="311" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H310" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6">
         <v>89</v>
       </c>
@@ -9136,8 +10048,11 @@
       <c r="G311" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="312" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H311" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6">
         <v>2825</v>
       </c>
@@ -9159,8 +10074,11 @@
       <c r="G312" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="313" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H312" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6">
         <v>2943</v>
       </c>
@@ -9182,8 +10100,11 @@
       <c r="G313" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="314" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H313" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6">
         <v>2751</v>
       </c>
@@ -9205,8 +10126,11 @@
       <c r="G314" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="315" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H314" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6">
         <v>2797</v>
       </c>
@@ -9228,8 +10152,11 @@
       <c r="G315" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="316" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H315" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6">
         <v>89</v>
       </c>
@@ -9251,8 +10178,11 @@
       <c r="G316" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="317" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H316" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
         <v>3257</v>
       </c>
@@ -9274,8 +10204,11 @@
       <c r="G317" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="318" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H317" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6">
         <v>2944</v>
       </c>
@@ -9297,8 +10230,11 @@
       <c r="G318" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="319" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H318" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6">
         <v>89</v>
       </c>
@@ -9320,8 +10256,11 @@
       <c r="G319" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="320" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H319" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6">
         <v>2796</v>
       </c>
@@ -9343,8 +10282,11 @@
       <c r="G320" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="321" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H320" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6">
         <v>2717</v>
       </c>
@@ -9366,8 +10308,11 @@
       <c r="G321" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="322" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H321" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6">
         <v>2931</v>
       </c>
@@ -9389,8 +10334,11 @@
       <c r="G322" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="323" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H322" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6">
         <v>2899</v>
       </c>
@@ -9412,8 +10360,11 @@
       <c r="G323" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="324" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H323" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6">
         <v>2904</v>
       </c>
@@ -9435,8 +10386,11 @@
       <c r="G324" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="325" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H324" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6">
         <v>2982</v>
       </c>
@@ -9458,8 +10412,11 @@
       <c r="G325" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="326" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H325" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6">
         <v>2844</v>
       </c>
@@ -9481,8 +10438,11 @@
       <c r="G326" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="327" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H326" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6">
         <v>2962</v>
       </c>
@@ -9504,8 +10464,11 @@
       <c r="G327" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="328" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H327" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6">
         <v>2859</v>
       </c>
@@ -9527,8 +10490,11 @@
       <c r="G328" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="329" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H328" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6">
         <v>2802</v>
       </c>
@@ -9550,8 +10516,11 @@
       <c r="G329" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="330" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H329" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6">
         <v>2920</v>
       </c>
@@ -9573,8 +10542,11 @@
       <c r="G330" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="331" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H330" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6">
         <v>3258</v>
       </c>
@@ -9596,8 +10568,11 @@
       <c r="G331" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="332" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H331" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6">
         <v>2846</v>
       </c>
@@ -9619,8 +10594,11 @@
       <c r="G332" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="333" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H332" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6">
         <v>3234</v>
       </c>
@@ -9642,8 +10620,11 @@
       <c r="G333" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="334" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H333" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6">
         <v>2741</v>
       </c>
@@ -9665,8 +10646,11 @@
       <c r="G334" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="335" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H334" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6">
         <v>89</v>
       </c>
@@ -9688,8 +10672,11 @@
       <c r="G335" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="336" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H335" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6">
         <v>2857</v>
       </c>
@@ -9711,8 +10698,11 @@
       <c r="G336" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="337" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H336" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6">
         <v>2779</v>
       </c>
@@ -9734,8 +10724,11 @@
       <c r="G337" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="338" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H337" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6">
         <v>89</v>
       </c>
@@ -9757,8 +10750,11 @@
       <c r="G338" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="339" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H338" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6">
         <v>2736</v>
       </c>
@@ -9780,8 +10776,11 @@
       <c r="G339" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="340" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H339" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6">
         <v>3027</v>
       </c>
@@ -9803,8 +10802,11 @@
       <c r="G340" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="341" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H340" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6">
         <v>89</v>
       </c>
@@ -9826,8 +10828,11 @@
       <c r="G341" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="342" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H341" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6">
         <v>2925</v>
       </c>
@@ -9849,8 +10854,11 @@
       <c r="G342" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="343" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H342" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6">
         <v>89</v>
       </c>
@@ -9872,8 +10880,11 @@
       <c r="G343" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="344" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H343" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6">
         <v>2863</v>
       </c>
@@ -9895,8 +10906,11 @@
       <c r="G344" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="345" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H344" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6">
         <v>2872</v>
       </c>
@@ -9918,8 +10932,11 @@
       <c r="G345" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="346" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H345" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6">
         <v>2890</v>
       </c>
@@ -9941,8 +10958,11 @@
       <c r="G346" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="347" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H346" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6">
         <v>2817</v>
       </c>
@@ -9964,8 +10984,11 @@
       <c r="G347" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="348" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H347" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6">
         <v>3099</v>
       </c>
@@ -9987,8 +11010,11 @@
       <c r="G348" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="349" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H348" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6">
         <v>2760</v>
       </c>
@@ -10010,8 +11036,11 @@
       <c r="G349" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H349" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6">
         <v>2731</v>
       </c>
@@ -10033,8 +11062,11 @@
       <c r="G350" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="351" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H350" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6">
         <v>2798</v>
       </c>
@@ -10056,8 +11088,11 @@
       <c r="G351" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="352" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H351" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6">
         <v>2813</v>
       </c>
@@ -10079,8 +11114,11 @@
       <c r="G352" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="353" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H352" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="353" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6">
         <v>3087</v>
       </c>
@@ -10102,8 +11140,11 @@
       <c r="G353" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="354" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H353" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="354" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6">
         <v>2839</v>
       </c>
@@ -10125,8 +11166,11 @@
       <c r="G354" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="355" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H354" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="355" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6">
         <v>2834</v>
       </c>
@@ -10148,8 +11192,11 @@
       <c r="G355" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="356" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H355" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="356" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6">
         <v>2725</v>
       </c>
@@ -10171,8 +11218,11 @@
       <c r="G356" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="357" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H356" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="357" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6">
         <v>3230</v>
       </c>
@@ -10194,8 +11244,11 @@
       <c r="G357" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="358" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H357" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="358" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6">
         <v>2932</v>
       </c>
@@ -10217,8 +11270,11 @@
       <c r="G358" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="359" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H358" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="359" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6">
         <v>2845</v>
       </c>
@@ -10240,8 +11296,11 @@
       <c r="G359" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H359" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="360" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6">
         <v>2879</v>
       </c>
@@ -10263,8 +11322,11 @@
       <c r="G360" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="361" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H360" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="361" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6">
         <v>89</v>
       </c>
@@ -10286,8 +11348,11 @@
       <c r="G361" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="362" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H361" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="362" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6">
         <v>3008</v>
       </c>
@@ -10309,8 +11374,11 @@
       <c r="G362" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="363" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H362" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="363" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6">
         <v>2888</v>
       </c>
@@ -10332,8 +11400,11 @@
       <c r="G363" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="364" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H363" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="364" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6">
         <v>2895</v>
       </c>
@@ -10355,8 +11426,11 @@
       <c r="G364" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="365" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H364" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="365" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6">
         <v>89</v>
       </c>
@@ -10378,8 +11452,11 @@
       <c r="G365" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="366" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H365" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="366" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6">
         <v>3216</v>
       </c>
@@ -10401,8 +11478,11 @@
       <c r="G366" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="367" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H366" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="367" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6">
         <v>2707</v>
       </c>
@@ -10424,8 +11504,11 @@
       <c r="G367" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="368" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H367" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="368" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6">
         <v>2766</v>
       </c>
@@ -10447,8 +11530,11 @@
       <c r="G368" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="369" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H368" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="369" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6">
         <v>3106</v>
       </c>
@@ -10470,8 +11556,11 @@
       <c r="G369" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="370" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H369" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="370" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6">
         <v>2921</v>
       </c>
@@ -10493,8 +11582,11 @@
       <c r="G370" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="371" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H370" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="371" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6">
         <v>2869</v>
       </c>
@@ -10516,8 +11608,11 @@
       <c r="G371" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="372" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H371" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="372" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6">
         <v>3231</v>
       </c>
@@ -10539,8 +11634,11 @@
       <c r="G372" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="373" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H372" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="373" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6">
         <v>89</v>
       </c>
@@ -10562,8 +11660,11 @@
       <c r="G373" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="374" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H373" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="374" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6">
         <v>2814</v>
       </c>
@@ -10585,8 +11686,11 @@
       <c r="G374" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="375" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H374" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="375" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6">
         <v>89</v>
       </c>
@@ -10608,8 +11712,11 @@
       <c r="G375" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="376" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H375" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="376" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6">
         <v>2772</v>
       </c>
@@ -10631,8 +11738,11 @@
       <c r="G376" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="377" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H376" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="377" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6">
         <v>2759</v>
       </c>
@@ -10654,8 +11764,11 @@
       <c r="G377" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="378" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H377" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="378" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6">
         <v>2758</v>
       </c>
@@ -10677,8 +11790,11 @@
       <c r="G378" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="379" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H378" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="379" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6">
         <v>2767</v>
       </c>
@@ -10700,8 +11816,11 @@
       <c r="G379" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="380" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H379" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="380" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6">
         <v>2757</v>
       </c>
@@ -10723,8 +11842,11 @@
       <c r="G380" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="381" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H380" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="381" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6">
         <v>3044</v>
       </c>
@@ -10746,8 +11868,11 @@
       <c r="G381" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="382" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H381" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="382" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6">
         <v>2761</v>
       </c>
@@ -10769,8 +11894,11 @@
       <c r="G382" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="383" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H382" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="383" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6">
         <v>2730</v>
       </c>
@@ -10792,8 +11920,11 @@
       <c r="G383" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="384" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H383" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="384" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6">
         <v>89</v>
       </c>
@@ -10815,8 +11946,11 @@
       <c r="G384" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="385" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H384" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="385" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6">
         <v>2769</v>
       </c>
@@ -10838,8 +11972,11 @@
       <c r="G385" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="386" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H385" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="386" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6">
         <v>2790</v>
       </c>
@@ -10861,8 +11998,11 @@
       <c r="G386" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="387" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H386" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="387" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6">
         <v>3233</v>
       </c>
@@ -10884,8 +12024,11 @@
       <c r="G387" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="388" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H387" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="388" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6">
         <v>2851</v>
       </c>
@@ -10907,8 +12050,11 @@
       <c r="G388" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="389" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H388" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="389" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6">
         <v>2924</v>
       </c>
@@ -10930,8 +12076,11 @@
       <c r="G389" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="390" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H389" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="390" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6">
         <v>89</v>
       </c>
@@ -10953,8 +12102,11 @@
       <c r="G390" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="391" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H390" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="391" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6">
         <v>89</v>
       </c>
@@ -10976,8 +12128,11 @@
       <c r="G391" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="392" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H391" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="392" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6">
         <v>2885</v>
       </c>
@@ -10999,8 +12154,11 @@
       <c r="G392" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="393" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H392" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="393" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6">
         <v>89</v>
       </c>
@@ -11022,8 +12180,11 @@
       <c r="G393" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="394" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H393" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="394" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6">
         <v>3021</v>
       </c>
@@ -11045,8 +12206,11 @@
       <c r="G394" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="395" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H394" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="395" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6">
         <v>2718</v>
       </c>
@@ -11068,8 +12232,11 @@
       <c r="G395" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="396" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H395" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="396" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6">
         <v>3013</v>
       </c>
@@ -11091,8 +12258,11 @@
       <c r="G396" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="397" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H396" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="397" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6">
         <v>89</v>
       </c>
@@ -11114,8 +12284,11 @@
       <c r="G397" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="398" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H397" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="398" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6">
         <v>3082</v>
       </c>
@@ -11137,8 +12310,11 @@
       <c r="G398" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="399" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H398" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="399" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6">
         <v>2752</v>
       </c>
@@ -11160,8 +12336,11 @@
       <c r="G399" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="400" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H399" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="400" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6">
         <v>2975</v>
       </c>
@@ -11183,8 +12362,11 @@
       <c r="G400" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="401" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H400" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="401" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6">
         <v>2734</v>
       </c>
@@ -11206,8 +12388,11 @@
       <c r="G401" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="402" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H401" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="402" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6">
         <v>3088</v>
       </c>
@@ -11229,8 +12414,11 @@
       <c r="G402" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="403" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H402" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="403" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6">
         <v>3252</v>
       </c>
@@ -11252,8 +12440,11 @@
       <c r="G403" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="404" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H403" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="404" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6">
         <v>89</v>
       </c>
@@ -11275,8 +12466,11 @@
       <c r="G404" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="405" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H404" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="405" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6">
         <v>89</v>
       </c>
@@ -11298,8 +12492,11 @@
       <c r="G405" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="406" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H405" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="406" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6">
         <v>2848</v>
       </c>
@@ -11321,8 +12518,11 @@
       <c r="G406" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="407" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H406" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="407" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6">
         <v>2680</v>
       </c>
@@ -11344,8 +12544,11 @@
       <c r="G407" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="408" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H407" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="408" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6">
         <v>2828</v>
       </c>
@@ -11367,8 +12570,11 @@
       <c r="G408" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="409" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H408" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="409" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6">
         <v>2823</v>
       </c>
@@ -11390,8 +12596,11 @@
       <c r="G409" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="410" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H409" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="410" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6">
         <v>2833</v>
       </c>
@@ -11413,8 +12622,11 @@
       <c r="G410" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="411" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H410" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="411" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6">
         <v>2905</v>
       </c>
@@ -11436,8 +12648,11 @@
       <c r="G411" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="412" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H411" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="412" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6">
         <v>89</v>
       </c>
@@ -11459,8 +12674,11 @@
       <c r="G412" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="413" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H412" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="413" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6">
         <v>2824</v>
       </c>
@@ -11482,8 +12700,11 @@
       <c r="G413" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="414" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H413" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="414" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6">
         <v>2735</v>
       </c>
@@ -11505,8 +12726,11 @@
       <c r="G414" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="415" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H414" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="415" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6">
         <v>2713</v>
       </c>
@@ -11528,8 +12752,11 @@
       <c r="G415" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="416" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H415" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="416" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6">
         <v>2950</v>
       </c>
@@ -11551,8 +12778,11 @@
       <c r="G416" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="417" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H416" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="417" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6">
         <v>89</v>
       </c>
@@ -11574,8 +12804,11 @@
       <c r="G417" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="418" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H417" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="418" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6">
         <v>3250</v>
       </c>
@@ -11597,8 +12830,11 @@
       <c r="G418" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="419" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H418" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="419" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6">
         <v>2968</v>
       </c>
@@ -11620,8 +12856,11 @@
       <c r="G419" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="420" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H419" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="420" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6">
         <v>3243</v>
       </c>
@@ -11643,8 +12882,11 @@
       <c r="G420" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="421" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H420" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="421" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6">
         <v>3259</v>
       </c>
@@ -11666,8 +12908,11 @@
       <c r="G421" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="422" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H421" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="422" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6">
         <v>3205</v>
       </c>
@@ -11689,8 +12934,11 @@
       <c r="G422" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="423" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H422" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="423" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6">
         <v>2791</v>
       </c>
@@ -11712,8 +12960,11 @@
       <c r="G423" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="424" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H423" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="424" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6">
         <v>3247</v>
       </c>
@@ -11735,8 +12986,11 @@
       <c r="G424" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="425" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H424" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="425" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6">
         <v>2963</v>
       </c>
@@ -11758,8 +13012,11 @@
       <c r="G425" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="426" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H425" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="426" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6">
         <v>3201</v>
       </c>
@@ -11781,8 +13038,11 @@
       <c r="G426" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="427" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H426" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="427" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6">
         <v>3202</v>
       </c>
@@ -11804,8 +13064,11 @@
       <c r="G427" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="428" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H427" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="428" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6">
         <v>2710</v>
       </c>
@@ -11827,8 +13090,11 @@
       <c r="G428" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="429" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H428" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="429" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6">
         <v>2711</v>
       </c>
@@ -11850,8 +13116,11 @@
       <c r="G429" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="430" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H429" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="430" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6">
         <v>2865</v>
       </c>
@@ -11873,8 +13142,11 @@
       <c r="G430" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="431" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H430" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="431" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6">
         <v>2928</v>
       </c>
@@ -11896,8 +13168,11 @@
       <c r="G431" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="432" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H431" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="432" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6">
         <v>2929</v>
       </c>
@@ -11919,8 +13194,11 @@
       <c r="G432" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="433" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H432" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="433" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6">
         <v>2690</v>
       </c>
@@ -11942,8 +13220,11 @@
       <c r="G433" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="434" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H433" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="434" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6">
         <v>2691</v>
       </c>
@@ -11965,8 +13246,11 @@
       <c r="G434" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="435" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H434" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="435" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6">
         <v>2976</v>
       </c>
@@ -11988,8 +13272,11 @@
       <c r="G435" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="436" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H435" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="436" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6">
         <v>89</v>
       </c>
@@ -12011,8 +13298,11 @@
       <c r="G436" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="437" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H436" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="437" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6">
         <v>3079</v>
       </c>
@@ -12034,8 +13324,11 @@
       <c r="G437" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="438" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H437" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="438" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6">
         <v>89</v>
       </c>
@@ -12057,8 +13350,11 @@
       <c r="G438" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="439" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H438" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="439" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6">
         <v>2753</v>
       </c>
@@ -12080,8 +13376,11 @@
       <c r="G439" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="440" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H439" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="440" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6">
         <v>3054</v>
       </c>
@@ -12103,8 +13402,11 @@
       <c r="G440" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="441" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H440" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="441" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6">
         <v>2967</v>
       </c>
@@ -12126,8 +13428,11 @@
       <c r="G441" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="442" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H441" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="442" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6">
         <v>3037</v>
       </c>
@@ -12149,8 +13454,11 @@
       <c r="G442" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="443" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H442" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="443" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6">
         <v>2909</v>
       </c>
@@ -12172,8 +13480,11 @@
       <c r="G443" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="444" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H443" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="444" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6">
         <v>2881</v>
       </c>
@@ -12195,8 +13506,11 @@
       <c r="G444" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="445" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H444" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="445" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6">
         <v>2936</v>
       </c>
@@ -12218,8 +13532,11 @@
       <c r="G445" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="446" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H445" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="446" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6">
         <v>2937</v>
       </c>
@@ -12241,8 +13558,11 @@
       <c r="G446" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="447" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H446" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="447" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6">
         <v>2873</v>
       </c>
@@ -12264,8 +13584,11 @@
       <c r="G447" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="448" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H447" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="448" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6">
         <v>2842</v>
       </c>
@@ -12287,8 +13610,11 @@
       <c r="G448" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="449" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H448" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="449" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6">
         <v>2933</v>
       </c>
@@ -12310,8 +13636,11 @@
       <c r="G449" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="450" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H449" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="450" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6">
         <v>2716</v>
       </c>
@@ -12333,8 +13662,11 @@
       <c r="G450" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="451" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H450" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="451" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6">
         <v>89</v>
       </c>
@@ -12356,8 +13688,11 @@
       <c r="G451" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="452" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H451" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="452" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6">
         <v>3059</v>
       </c>
@@ -12379,8 +13714,11 @@
       <c r="G452" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="453" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H452" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="453" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6">
         <v>3219</v>
       </c>
@@ -12402,8 +13740,11 @@
       <c r="G453" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="454" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H453" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="454" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6">
         <v>3210</v>
       </c>
@@ -12425,8 +13766,11 @@
       <c r="G454" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="455" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H454" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="455" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6">
         <v>3261</v>
       </c>
@@ -12448,8 +13792,11 @@
       <c r="G455" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="456" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H455" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="456" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6">
         <v>2708</v>
       </c>
@@ -12471,8 +13818,11 @@
       <c r="G456" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="457" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H456" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="457" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6">
         <v>2777</v>
       </c>
@@ -12494,8 +13844,11 @@
       <c r="G457" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="458" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H457" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="458" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6">
         <v>3085</v>
       </c>
@@ -12517,8 +13870,11 @@
       <c r="G458" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="459" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H458" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="459" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6">
         <v>2781</v>
       </c>
@@ -12540,8 +13896,11 @@
       <c r="G459" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="460" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H459" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="460" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6">
         <v>2854</v>
       </c>
@@ -12563,8 +13922,11 @@
       <c r="G460" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="461" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H460" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="461" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6">
         <v>2768</v>
       </c>
@@ -12586,8 +13948,11 @@
       <c r="G461" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="462" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H461" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="462" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6">
         <v>89</v>
       </c>
@@ -12609,8 +13974,11 @@
       <c r="G462" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="463" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H462" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="463" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6">
         <v>3033</v>
       </c>
@@ -12632,8 +14000,11 @@
       <c r="G463" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="464" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H463" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="464" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6">
         <v>3034</v>
       </c>
@@ -12655,8 +14026,11 @@
       <c r="G464" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="465" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H464" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="465" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6">
         <v>3061</v>
       </c>
@@ -12678,8 +14052,11 @@
       <c r="G465" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="466" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H465" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="466" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6">
         <v>3218</v>
       </c>
@@ -12701,8 +14078,11 @@
       <c r="G466" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="467" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H466" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="467" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6">
         <v>2788</v>
       </c>
@@ -12724,8 +14104,11 @@
       <c r="G467" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="468" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H467" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="468" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6">
         <v>3220</v>
       </c>
@@ -12747,8 +14130,11 @@
       <c r="G468" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="469" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H468" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="469" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6">
         <v>3055</v>
       </c>
@@ -12770,8 +14156,11 @@
       <c r="G469" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="470" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H469" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="470" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6">
         <v>3215</v>
       </c>
@@ -12793,8 +14182,11 @@
       <c r="G470" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="471" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H470" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="471" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6">
         <v>3253</v>
       </c>
@@ -12816,8 +14208,11 @@
       <c r="G471" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="472" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H471" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="472" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6">
         <v>2871</v>
       </c>
@@ -12839,8 +14234,11 @@
       <c r="G472" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="473" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H472" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="473" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6">
         <v>2940</v>
       </c>
@@ -12862,8 +14260,11 @@
       <c r="G473" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="474" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H473" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="474" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6">
         <v>2941</v>
       </c>
@@ -12885,8 +14286,11 @@
       <c r="G474" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="475" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H474" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="475" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6">
         <v>3235</v>
       </c>
@@ -12908,8 +14312,11 @@
       <c r="G475" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="476" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H475" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="476" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6">
         <v>2737</v>
       </c>
@@ -12931,8 +14338,11 @@
       <c r="G476" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="477" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H476" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="477" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6">
         <v>3028</v>
       </c>
@@ -12954,8 +14364,11 @@
       <c r="G477" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="478" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H477" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="478" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6">
         <v>89</v>
       </c>
@@ -12977,8 +14390,11 @@
       <c r="G478" s="2" t="s">
         <v>350</v>
       </c>
-    </row>
-    <row r="479" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H478" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="479" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6">
         <v>2792</v>
       </c>
@@ -13000,8 +14416,11 @@
       <c r="G479" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="480" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H479" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="480" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6">
         <v>89</v>
       </c>
@@ -13023,8 +14442,11 @@
       <c r="G480" s="2" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="481" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H480" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="481" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6">
         <v>2900</v>
       </c>
@@ -13045,13 +14467,16 @@
       </c>
       <c r="G481" s="2" t="s">
         <v>350</v>
+      </c>
+      <c r="H481" t="s">
+        <v>487</v>
       </c>
     </row>
   </sheetData>
   <sortState ref="A2:G485">
     <sortCondition ref="B291"/>
   </sortState>
-  <conditionalFormatting sqref="B1:E1048576">
+  <conditionalFormatting sqref="B1:E1048576 H1">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
